--- a/bom/Fall_Protection_Vest_BOM.xlsx
+++ b/bom/Fall_Protection_Vest_BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phongtruong2003/Desktop/Inflate Body/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phongtruong2003/Desktop/Inflate Body/Documetaion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9547E43-FD0F-8C46-B3E8-509CFAF02A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D2EEED-1139-F64B-BFCF-6BE6F01D80B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17100" yWindow="680" windowWidth="17100" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EE BOM" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="67">
   <si>
     <t>Note: Shipping, tax, not included.</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Buy Now / Later</t>
-  </si>
-  <si>
     <t>Team Owner</t>
   </si>
   <si>
@@ -74,27 +71,18 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>Price Checked</t>
-  </si>
-  <si>
     <t>Controller</t>
   </si>
   <si>
     <t>DigiKey</t>
   </si>
   <si>
-    <t>Buy Now</t>
-  </si>
-  <si>
     <t>Firmware / MCU / IMU</t>
   </si>
   <si>
     <t>In stock</t>
   </si>
   <si>
-    <t>9/3/2026</t>
-  </si>
-  <si>
     <t>Sensor</t>
   </si>
   <si>
@@ -125,9 +113,6 @@
     <t>Power</t>
   </si>
   <si>
-    <t>Buy Later</t>
-  </si>
-  <si>
     <t>Power / Circuits</t>
   </si>
   <si>
@@ -170,27 +155,15 @@
     <t>Optional / Future Features</t>
   </si>
   <si>
-    <t>9/8/2026</t>
-  </si>
-  <si>
-    <t>NEO-6M GPS module</t>
-  </si>
-  <si>
     <t>Category subtotal</t>
   </si>
   <si>
     <t>EE material total</t>
   </si>
   <si>
-    <t>https://www.amazon.com/YELUFT-GY-NEO6MV2-Control-Support-Raspberry/dp/B0F2DKWJ4J/ref=sr_1_5?crid=116EGIA65O3RM&amp;dib=eyJ2IjoiMSJ9._JPp2AFGHWD_4dT5XNP-SnycfWRcMEOIub2ZYPONWQCLCLeiU7IqwyEKS3O7elcKxsS4py1gFeZ29XIWHm3QTQ3QX_M8mEECUlKve1ZeAJ8Sea1zyersA8alZieFz783-0tomvuy7tnT7_plsjbRSkmZne4iC7YSXRxw8aODNDlKrBKc52KSxYyvh4mKNzSCc9jvfxMSm6pLkugQCZksvUxxBY3AoB3QW4X--jUrNn5T5i-aCIDrq5RVg4QEaVsgrToN-ionJzHsbWyn2QLOyEeYSgOXiigk-v-RNM3CDFg.Pa5G0Wery0aCEinKh-zrDlm7cRXMrO8CM8Sp6U33dIg&amp;dib_tag=se&amp;keywords=neo%2B6m&amp;qid=1788912414&amp;sprefix=%2Caps%2C165&amp;sr=8-5&amp;th=1</t>
-  </si>
-  <si>
     <t>GPS</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
     <t>One IMU only.</t>
   </si>
   <si>
@@ -227,9 +200,6 @@
     <t>Mechanical Decision</t>
   </si>
   <si>
-    <t>5 V regulator</t>
-  </si>
-  <si>
     <t>Make 5 V power for MCU</t>
   </si>
   <si>
@@ -237,16 +207,44 @@
   </si>
   <si>
     <t>Mech</t>
+  </si>
+  <si>
+    <t>LTE</t>
+  </si>
+  <si>
+    <t>ATGM336H</t>
+  </si>
+  <si>
+    <t>https://muzi.works/products/gps-module-atgm336h?variant=44042070687801&amp;country=US&amp;currency=USD&amp;utm_medium=product_sync&amp;utm_source=google&amp;utm_content=sag_organic&amp;utm_campaign=sag_organic&amp;srsltid=AU7gw4W8_U6VfNOJbK2s0PzxtFfZdaGhkCuRvhFiX4sgV-jsOcUr4_YRrUI</t>
+  </si>
+  <si>
+    <t>Muzi works</t>
+  </si>
+  <si>
+    <t>https://m.elecrow.com/pages/shop/product/details?id=207633&amp;srsltid=AU7gw4WkNELzGttMYB8k4pEBEveqoDqMXXPwLDrxFddl8cz2gcexXqbK</t>
+  </si>
+  <si>
+    <t>Instock</t>
+  </si>
+  <si>
+    <t>Temporary because the one we aim is out of stock</t>
+  </si>
+  <si>
+    <t>SIM7670</t>
+  </si>
+  <si>
+    <t>Data Module</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -284,13 +282,24 @@
       <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Carlito"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -315,7 +324,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -347,9 +356,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -357,6 +364,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -373,6 +386,104 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1248480</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>683160</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1248840</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>683520</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CECFF21-6239-8F66-9C99-A37E906DB8C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="1248480" y="4035960"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CECFF21-6239-8F66-9C99-A37E906DB8C2}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1242360" y="4029840"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-10-18T21:41:28.806"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+      <inkml:brushProperty name="color" value="#E71224"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'0'0'0</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -581,16 +692,14 @@
     <col min="6" max="6" width="11" customWidth="1"/>
     <col min="7" max="7" width="9" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="19">
+    <row r="1" spans="1:11" ht="19">
       <c r="A1" s="16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B1" s="16"/>
       <c r="C1" s="16"/>
@@ -602,10 +711,8 @@
       <c r="I1" s="16"/>
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-    </row>
-    <row r="2" spans="1:13" ht="15">
+    </row>
+    <row r="2" spans="1:11" ht="15">
       <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
@@ -619,10 +726,8 @@
       <c r="I2" s="17"/>
       <c r="J2" s="17"/>
       <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-    </row>
-    <row r="4" spans="1:13" ht="15">
+    </row>
+    <row r="4" spans="1:11" ht="15">
       <c r="A4" s="18" t="s">
         <v>1</v>
       </c>
@@ -632,14 +737,12 @@
       <c r="E4" s="18"/>
       <c r="F4" s="2"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="18"/>
+      <c r="H4" s="1"/>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-    </row>
-    <row r="6" spans="1:13" ht="48" customHeight="1">
+      <c r="K4" s="1"/>
+    </row>
+    <row r="6" spans="1:11" ht="48" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -653,7 +756,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>6</v>
@@ -673,28 +776,22 @@
       <c r="K6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="69.25" customHeight="1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="69.25" customHeight="1">
-      <c r="A7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="7" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F7" s="5">
         <v>12.95</v>
@@ -707,36 +804,30 @@
         <v>12.95</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K7" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="69.25" customHeight="1">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M7" s="15">
-        <v>46301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="69.25" customHeight="1">
-      <c r="A8" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="B8" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F8" s="5">
         <v>0.95</v>
@@ -749,36 +840,28 @@
         <v>0.95</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="69.25" customHeight="1">
-      <c r="A9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="69.25" customHeight="1">
+      <c r="A9" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F9" s="5">
         <v>2.25</v>
@@ -791,36 +874,30 @@
         <v>2.25</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="69.25" customHeight="1">
+      <c r="A10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="C10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="69.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="F10" s="5">
         <v>2.88</v>
@@ -833,65 +910,57 @@
         <v>2.88</v>
       </c>
       <c r="I10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="69.25" customHeight="1">
+      <c r="A11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="69.25" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="7" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6">
         <v>1</v>
       </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:13" ht="69.25" customHeight="1">
+      <c r="I11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="69.25" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="F12" s="10">
         <f>19.99/3</f>
@@ -905,78 +974,91 @@
         <v>19.989999999999998</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="9" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="69.25" customHeight="1">
+    <row r="13" spans="1:11" ht="69.25" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F13" s="10">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="G13" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="10">
-        <f>11.99</f>
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="B14" t="str">
-        <f t="shared" ref="B14:B21" si="1">""</f>
+        <v>42</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30">
+      <c r="A14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="5">
+        <v>22.69</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="20">
+        <v>22.69</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" t="str">
+        <f t="shared" ref="B15:B21" si="1">""</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="B15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15">
+    <row r="16" spans="1:11" ht="15">
       <c r="A16" s="13" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B16" s="14" t="str">
         <f t="shared" si="1"/>
@@ -985,7 +1067,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" s="12" t="str">
         <f t="shared" si="1"/>
@@ -994,7 +1076,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B18" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1003,7 +1085,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B19" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1012,7 +1094,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B20" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1021,7 +1103,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B21" s="12" t="str">
         <f t="shared" si="1"/>
@@ -1030,7 +1112,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B22" s="12">
         <f>SUMIF($A$7:$A$13,A22,$H$7:$H$13)</f>
@@ -1039,7 +1121,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B23" s="12">
         <f>SUMIF($A$7:$A$13,A23,$H$7:$H$13)</f>
@@ -1048,7 +1130,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B24" s="12">
         <f>SUMIF($A$7:$A$13,A24,$H$7:$H$13)</f>
@@ -1057,7 +1139,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="8" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B25" s="12">
         <f>SUMIF($A$7:$A$13,A25,$H$7:$H$13)</f>
@@ -1070,27 +1152,23 @@
     </row>
     <row r="27" spans="1:2" ht="15">
       <c r="A27" s="13" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B27" s="14">
-        <f>SUM($H$7:$H$13)</f>
-        <v>51.01</v>
+        <f>SUM($H$7:$H$14)</f>
+        <v>71.7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A2:M2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="I4:J4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" sqref="I7:I13" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>"Buy Now,Buy Later"</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="J7:J13" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="I7:I13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"EE Lead,Firmware / MCU / IMU,Power / Circuits,PCB / Hardware"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1101,7 +1179,10 @@
     <hyperlink ref="E10" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
     <hyperlink ref="E12" r:id="rId5" xr:uid="{59F68FD3-216E-984C-8AA4-3C41D0297640}"/>
     <hyperlink ref="E11" r:id="rId6" xr:uid="{FE57CD68-7C12-C649-9621-E15353D769C3}"/>
+    <hyperlink ref="E13" r:id="rId7" xr:uid="{B3E8E3AB-C6C1-3146-9116-0E5763DA8F5C}"/>
+    <hyperlink ref="E14" r:id="rId8" xr:uid="{24A430F8-8018-AA44-8F51-4FB8DD57F239}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>